--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6548-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6548-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFF00F3E-67A4-4473-9AFE-DE980694DAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{629D3E2E-BDAE-4C6F-8CB1-F46EE7A9AC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0514BE8E-AF8D-4C27-8F42-7F5942E50B62}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{CF88ED4E-4141-4FE2-B310-FEFD6D3225B8}"/>
   </bookViews>
   <sheets>
     <sheet name="6548-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1558,28 +1558,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5AA2BB-DF1F-4BB2-A1A9-A034E8FB0A30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A567D4C-94ED-4F0C-8532-F8FF576B8C7D}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1613,7 +1613,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1769,7 +1769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1877,7 +1877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>2024</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>29</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2023</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2022</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2021</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="47">
         <v>2020</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>29</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>29</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="49">
         <v>2019</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>2018</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="49">
         <v>2017</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>2016</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="49">
         <v>2015</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>2014</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="49" t="s">
         <v>59</v>
       </c>
